--- a/scripts/statistiche.xlsx
+++ b/scripts/statistiche.xlsx
@@ -9,17 +9,24 @@
   <sheets>
     <sheet name="Value_Function" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Gradients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gradients_Zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IoU" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Value_Function'!$A$1:$H$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gradients'!$A$1:$H$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gradients_Zero'!$A$1:$H$16</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.00&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -62,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -74,6 +81,16 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,10 +456,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -802,7 +819,736 @@
         <v>1.220108758907755</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Rapporto unsafe BRT/V0</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2.253084766724623</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1.142560841206524</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2.011190283987415</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1.044568143673676</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1.11991824936312</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1.120554311548291</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1.326606840506202</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BRT percentile 3 (97% &gt;= soglia)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-2.643425703048706</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-2.836691379547119</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-1.701006531715393</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.2000868916511536</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-3.026782989501953</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-1.001716017723083</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>-2.995643615722656</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>V0 min state: x_rel</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1.000000476837158</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>V0 min state: y_rel</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>V0 min state: theta_rel</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-1.963495492935181</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-1.963495492935181</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-3.010693073272705</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-3.141592741012573</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0.7853982448577881</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.5235989689826965</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-0.6544983983039856</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>V0 min state: v_H</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>6.714285850524902</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>V0 min state: delta_E</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.05235988646745682</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.1047197580337524</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>V0 min state: v_E</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>V0 max state: x_rel</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>V0 max state: y_rel</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>V0 max state: theta_rel</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-1.963495492935181</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1.047197699546814</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-3.141592741012573</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-3.141592741012573</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-3.141592741012573</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-3.141592741012573</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>-1.963495492935181</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>V0 max state: v_H</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>V0 max state: delta_E</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.2617993950843811</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.2617993950843811</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>V0 max state: v_E</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>BRT min state: x_rel</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>5.000000476837158</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>5.000000476837158</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>5.000000476837158</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>BRT min state: y_rel</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>BRT min state: theta_rel</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.5235987305641174</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.3926990628242493</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.3926990628242493</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.6544985175132751</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-0.6544983983039856</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>-0.6544983983039856</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BRT min state: v_H</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>BRT min state: delta_E</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0.2617993950843811</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0.1047197580337524</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.2617993950843811</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>BRT min state: v_E</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>BRT max state: x_rel</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>BRT max state: y_rel</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>BRT max state: theta_rel</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>1.178097248077393</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1.047197699546814</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>-3.141592741012573</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-3.141592741012573</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>-3.141592741012573</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>-3.141592741012573</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>-1.963495492935181</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>BRT max state: v_H</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>BRT max state: delta_E</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0.2617993950843811</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0.2617993950843811</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-0.2617993950843811</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.2617993950843811</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>BRT max state: v_E</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:H38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -813,10 +1559,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -871,337 +1617,2427 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>dBRT/dx_rel min</t>
+          <t>dV0/dx_rel min</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-5.240486145019531</v>
+        <v>-1.038817405700684</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>-7.274077892303467</v>
+        <v>-1.107488393783569</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-7.781867980957031</v>
+        <v>-3.597241878509521</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-2.501834392547607</v>
+        <v>-0.8759102821350098</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-33.87802124023438</v>
+        <v>-5.3125</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-1.994834184646606</v>
+        <v>-0.6666666269302368</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>-7.548908710479736</v>
+        <v>-1.149796724319458</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>dBRT/dx_rel max</t>
+          <t>dV0/dx_rel max</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.83003044128418</v>
+        <v>1.038817763328552</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10.57686042785645</v>
+        <v>1.190713763237</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>7.035525321960449</v>
+        <v>3.244303226470947</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2.643916368484497</v>
+        <v>0.8890361189842224</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>36.34697723388672</v>
+        <v>5.443750381469727</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2.420215129852295</v>
+        <v>0.6666666269302368</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>8.614456176757812</v>
+        <v>1.189308404922485</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>dBRT/dy_rel min</t>
+          <t>dV0/dx_rel std</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-13.21490859985352</v>
+        <v>0.7387664842364711</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-15.64837455749512</v>
+        <v>0.6836679792878158</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-7.218051910400391</v>
+        <v>0.3287536518527333</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-4.966061115264893</v>
+        <v>0.1045052371924917</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-52.128662109375</v>
+        <v>0.6218011610657158</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-4.765932559967041</v>
+        <v>0.1239041577342858</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-13.28059196472168</v>
+        <v>0.7188891851377142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>dBRT/dy_rel max</t>
+          <t>dBRT/dx_rel min</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>13.21492862701416</v>
+        <v>-5.240486145019531</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>15.64836120605469</v>
+        <v>-7.274077892303467</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7.218062400817871</v>
+        <v>-7.781867980957031</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4.966068267822266</v>
+        <v>-2.501834392547607</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>52.12871170043945</v>
+        <v>-33.87802124023438</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4.765939712524414</v>
+        <v>-1.994834184646606</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>13.2805814743042</v>
+        <v>-7.548908710479736</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>dBRT/dtheta_rel min</t>
+          <t>dBRT/dx_rel max</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-53.50682067871094</v>
+        <v>9.83003044128418</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-62.64264678955078</v>
+        <v>10.57686042785645</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-42.29959106445312</v>
+        <v>7.035525321960449</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-23.08028221130371</v>
+        <v>2.643916368484497</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-257.4273681640625</v>
+        <v>36.34697723388672</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-17.76876831054688</v>
+        <v>2.420215129852295</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-69.42903137207031</v>
+        <v>8.614456176757812</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>dBRT/dtheta_rel max</t>
+          <t>dBRT/dx_rel std</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>53.50745391845703</v>
+        <v>0.71337271273985</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>62.64614868164062</v>
+        <v>0.6930080353613904</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>42.29949188232422</v>
+        <v>0.400876201777372</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>23.08029174804688</v>
+        <v>0.1003010882185484</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>257.4276733398438</v>
+        <v>0.6394390508305422</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>17.76878547668457</v>
+        <v>0.1294454442170195</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>69.42910003662109</v>
+        <v>0.728756293939324</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>dBRT/dv_H min</t>
+          <t>dDelta/dx_rel std</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-5.849353790283203</v>
+        <v>0.3504288870168228</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-4.468188285827637</v>
+        <v>0.1906043007408972</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-2.857809782028198</v>
+        <v>0.2130796780890599</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-0.8638044595718384</v>
+        <v>0.04938357909607106</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-4.73747730255127</v>
+        <v>0.466730403051541</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-1.078449249267578</v>
+        <v>0.05893048404293766</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-6.004041194915771</v>
+        <v>0.2460878904460308</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>dBRT/dv_H max</t>
+          <t>dDelta/dx_rel mean abs</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>6.609495162963867</v>
+        <v>0.2030063427858804</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>8.51025390625</v>
+        <v>0.06468324050505993</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.218192100524902</v>
+        <v>0.08794623680023358</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3.091545581817627</v>
+        <v>0.01507583635632891</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>39.40787124633789</v>
+        <v>0.1488867666687185</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2.799252986907959</v>
+        <v>0.02295242875765881</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>7.834670543670654</v>
+        <v>0.09825804640304259</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>dBRT/ddelta_E min</t>
+          <t>dV0/dy_rel min</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-139.0772399902344</v>
+        <v>-1.013864517211914</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-151.0079803466797</v>
+        <v>-1.315361976623535</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-86.72346496582031</v>
+        <v>-3.561692237854004</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-96.07835388183594</v>
+        <v>-0.8870176076889038</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-690.4173583984375</v>
+        <v>-6</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-43.41152191162109</v>
+        <v>-0.6666666269302368</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-144.7698211669922</v>
+        <v>-1.332064390182495</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>dBRT/ddelta_E max</t>
+          <t>dV0/dy_rel max</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>139.0768127441406</v>
+        <v>1.013864517211914</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>151.0079498291016</v>
+        <v>1.315361976623535</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>86.72370910644531</v>
+        <v>3.561692237854004</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>96.07835388183594</v>
+        <v>0.8870176076889038</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>690.4168090820312</v>
+        <v>6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>43.41159057617188</v>
+        <v>0.6666666269302368</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>144.7698364257812</v>
+        <v>1.332064867019653</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>dBRT/dv_E min</t>
+          <t>dV0/dy_rel std</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-2.649695158004761</v>
+        <v>0.618256961090672</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-2.652986526489258</v>
+        <v>0.6658824342275497</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-2.14587140083313</v>
+        <v>0.4116815913412114</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.6255459785461426</v>
+        <v>0.1305122239804957</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-5.686383247375488</v>
+        <v>0.7769847332610127</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.7157508134841919</v>
+        <v>0.1706240212265292</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.720942974090576</v>
+        <v>0.6745333090047392</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>dBRT/dy_rel min</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-13.21490859985352</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-15.64837455749512</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-7.218051910400391</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-4.966061115264893</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-52.128662109375</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-4.765932559967041</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>-13.28059196472168</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/dy_rel max</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>13.21492862701416</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>15.64836120605469</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>7.218062400817871</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>4.966068267822266</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>52.12871170043945</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>4.765939712524414</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>13.2805814743042</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/dy_rel std</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0.6772534391214938</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.6883783459801444</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.516792157702735</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.1253596881436166</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.8039587937967438</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.1711854649437542</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.7033851848998973</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dy_rel std</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0.3775124362932857</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.2067180915741968</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.2658939617307109</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.06101888985907618</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.540500610591833</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.07552107253120269</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.266579108008857</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dy_rel mean abs</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0.2062133874011238</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0.06577812943168604</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.1097565404966736</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.01896067854127559</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.1781755561497944</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.02922003840782708</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.1015366997810513</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>dV0/dtheta_rel min</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-2.012054443359375</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-14.394775390625</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-28.97617340087891</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-4.126818180084229</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-33.01321411132812</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-4.321876525878906</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-12.55522537231445</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>dV0/dtheta_rel max</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.0814368724823</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>14.39476299285889</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>28.97617340087891</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>4.126818656921387</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>33.01320648193359</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>4.321876525878906</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>12.55521392822266</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>dV0/dtheta_rel std</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.9997392772419011</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2.800841106359267</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1.759517376800476</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.5611334418344081</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>3.939393000119033</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.7813404772604258</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>2.391673083074451</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/dtheta_rel min</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-53.50682067871094</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>-62.64264678955078</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>-42.29959106445312</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-23.08028221130371</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-257.4273681640625</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-17.76876831054688</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>-69.42903137207031</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/dtheta_rel max</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>53.50745391845703</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>62.64614868164062</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>42.29949188232422</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>23.08029174804688</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>257.4276733398438</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>17.76878547668457</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>69.42910003662109</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/dtheta_rel std</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>3.672888375295045</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>3.608192069630133</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2.608431921285178</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.6087626073309083</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>3.978158076428114</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>1.031175440842042</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>3.952472001168654</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dtheta_rel std</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>3.483216142769266</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1.891521670527827</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1.799123377134876</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.4018245258470313</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>3.081936647770214</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.6026800776170496</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>2.641128762339223</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dtheta_rel mean abs</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1.74839368279149</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.6080124196427177</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.6820622614461361</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.1215777884083215</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1.049946757872378</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.2312330741997956</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.9782433644483729</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>dV0/dv_H min</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>-1.30780017375946</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>-2.075889587402344</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-0.628861665725708</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-4.199999809265137</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-0.4666666388511658</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>-1.557028889656067</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>dV0/dv_H max</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1.185272574424744</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>2.084789991378784</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.6267087459564209</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>4.199999809265137</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.4666666388511658</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>1.469387292861938</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>dV0/dv_H std</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.2933560577075908</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.1697126558301191</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.05494036507429971</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.4465241962178781</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.06283729406127915</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0.2681696257916157</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/dv_H min</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>-5.849353790283203</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-4.468188285827637</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-2.857809782028198</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.8638044595718384</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-4.73747730255127</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-1.078449249267578</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>-6.004041194915771</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/dv_H max</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>6.609495162963867</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>8.51025390625</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>4.218192100524902</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>3.091545581817627</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>39.40787124633789</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>2.799252986907959</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>7.834670543670654</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/dv_H std</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>0.2845620908880984</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0.3102818861873675</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0.1819280235441677</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.04692997322708029</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.4070629672735324</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.05564340021494622</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.2918090365624607</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dv_H std</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>0.2845620908880984</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>0.1605932734003691</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.1400531713696012</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.04172257865484577</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.3689771350782923</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.05611056570365297</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.2427464198434916</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dv_H mean abs</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0.1173224195425035</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>0.05915051589052149</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0.05196770752406384</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.0113268927366939</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.1114880060591936</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.01720890779094381</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.08929459081546925</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>dV0/ddelta_E min</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>-42.25307464599609</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>-56.94588851928711</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-17.22355461120605</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>-114.5915451049805</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>-12.73239421844482</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>-30.23514556884766</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>dV0/ddelta_E max</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>42.25306701660156</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>56.94589233398438</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>17.22355461120605</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>114.5915451049805</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>12.73239421844482</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>30.23513793945312</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>dV0/ddelta_E std</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>5.741299945926415</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3.828894877033418</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1.187190984355097</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>10.14196234364367</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>1.793010701005112</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>4.001714241922417</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/ddelta_E min</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>-139.0772399902344</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>-151.0079803466797</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>-86.72346496582031</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-96.07835388183594</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>-690.4173583984375</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-43.41152191162109</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>-144.7698211669922</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/ddelta_E max</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>139.0768127441406</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>151.0079498291016</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>86.72370910644531</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>96.07835388183594</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>690.4168090820312</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>43.41159057617188</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>144.7698364257812</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/ddelta_E std</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>4.786135587943702</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>6.64378731327813</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4.089913668050611</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1.131886092061527</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>9.951798586038509</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1.791910569431657</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>5.100906248812499</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/ddelta_E std</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>4.786135587943702</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2.860876635732665</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>3.062536788557018</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.8917906638587334</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>8.003421940412622</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0.8560907953820648</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>2.939696949211023</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/ddelta_E mean abs</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>2.067740660408567</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.9904020551677614</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1.071238187669896</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.232302452316416</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>2.532026005855189</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.2671090917865809</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.9972718507726712</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>dV0/dv_E min</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>-1.302965879440308</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>-2.095406293869019</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.6292925477027893</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>-4.199999809265137</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>-0.4666666388511658</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>-1.599875211715698</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>dV0/dv_E max</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1.206440925598145</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>2.082431554794312</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0.6246451139450073</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>4.199999809265137</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.4666666388511658</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>1.469387054443359</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>dV0/dv_E std</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0.323082878153703</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0.1644004740603224</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.05746812096148624</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.4187077367990014</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.08434088899908511</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0.3228903165076512</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/dv_E min</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>-2.649695158004761</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>-2.652986526489258</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>-2.14587140083313</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-0.6255459785461426</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>-5.686383247375488</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>-0.7157508134841919</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>-2.720942974090576</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>dBRT/dv_E max</t>
         </is>
       </c>
+      <c r="B46" s="3" t="n">
+        <v>11.65330123901367</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>14.19045066833496</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>6.291808128356934</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>5.336698532104492</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>70.27783203125</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>4.499393463134766</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>12.68283843994141</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>dBRT/dv_E std</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0.3528163007420319</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0.3760264247258183</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0.2388798353667227</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.06017289240132732</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.5099751148595552</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.09055344011422717</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0.3820252104236123</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dv_E std</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>0.3528163007420319</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.2023882921905124</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.1873632909207818</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.04577581103209925</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.5049980018061544</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.05013057437556955</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.2372514022004204</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dv_E mean abs</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>0.1912742207791399</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.07126070604592018</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.07390156381131989</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.01270438701243784</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.1213880584036914</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.01687235984392897</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.09914472648235206</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H49"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Statistica</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>euclidean</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dce</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ttc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>eggert</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>time_eggert</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>sff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Epsilon |BRT|</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>N punti vicino a BRT=0</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1188376</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1260190</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1033583</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>4552422</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>424482</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>4532097</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1165604</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Punti vicino a BRT=0 [%]</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>6.895564096850862</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>7.312265578579916</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>5.99737610479798</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>26.41547599153298</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>2.463061218805704</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>26.29753996769162</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>6.763429330065359</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dx_rel std</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0.4843998531232814</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.2543016264877556</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.3730669397799572</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.08307220607870126</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.7736868257801206</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.08544211516526402</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0.3535538371174788</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dx_rel mean abs</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0.3431722823098779</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.1066648339499495</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.2686827998098372</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.03786570829981797</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.5607390168005424</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.04338629058215109</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.1757994954448453</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dy_rel std</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.518746902051563</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.2665958474775956</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.3891951803638535</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.1016245619233429</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.9648284436720319</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.09693895182555354</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.3684009848943134</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dy_rel mean abs</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0.3268860968876243</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.1082778397091417</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.2815548382770485</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.04691286138024853</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.6596924737121942</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.0469186976293554</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.1703041797071011</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dtheta_rel std</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>4.780621822625008</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2.470341895393967</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3.163347463809105</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.6375651055927954</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>5.766320793596748</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.9052904069928991</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>3.695528183630298</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dtheta_rel mean abs</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2.71984241699691</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.9462305971000551</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2.04702176910366</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.2755798543623225</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>3.94195530550947</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.4385176296530078</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1.672373979904668</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dv_H std</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0.3121973694914551</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.1722421042009897</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.2116799424195799</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.07160749469628007</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.7238440431605606</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.06793971272463907</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.2826919892277919</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dv_H mean abs</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0.1516810392138416</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.0756404751455669</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.1215205447203009</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.02957673328439307</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.4794863576370345</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.02349042718543524</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.1260107331206038</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/ddelta_E std</t>
+        </is>
+      </c>
       <c r="B13" s="3" t="n">
-        <v>11.65330123901367</v>
+        <v>6.502633910055283</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>14.19045066833496</v>
+        <v>3.792755824313982</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>6.291808128356934</v>
+        <v>5.757700067850146</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5.336698532104492</v>
+        <v>1.451612414108644</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>70.27783203125</v>
+        <v>15.94613163030576</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>4.499393463134766</v>
+        <v>1.240609058458947</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12.68283843994141</v>
+        <v>4.354598874785506</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/ddelta_E mean abs</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>3.2220414200203</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1.550232817207393</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>3.126446637831327</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.5394992155977397</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>10.69366908465516</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.5005413939115224</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.843045306211183</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dv_E std</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0.3937710351641709</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.2278532257058653</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.2724755024077647</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.06807934480804095</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.5551619133017544</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.06647847448111195</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.3119211377248772</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>dDelta/dv_E mean abs</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0.2094192460723222</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.09586818175652728</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.1808852050950096</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.0276612306892653</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.3975180878766955</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.03003030679778298</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.1481766422706658</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>BRT unsafe IoU</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>euclidean</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>dce</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>ttc</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>eggert</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>time_eggert</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>sff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>euclidean</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>0.9108544260556372</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>0.8813162848196847</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>0.8859761313668889</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>0.7485057409870638</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>0.5669697880104639</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>0.9661412809060678</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dce</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>0.9108544260556372</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0.8153509528750928</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0.9059672685393528</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>0.8172091617888804</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>0.6145302218207954</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>0.9069803774124751</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ttc</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>0.8813162848196847</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>0.8153509528750928</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>0.850827181890391</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.6705758433631502</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.505982188986663</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0.8585757865210202</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eggert</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>0.8859761313668889</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>0.9059672685393528</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0.850827181890391</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.7547997154957112</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.5697470750107609</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0.8748414065097995</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>time_eggert</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>0.7485057409870638</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>0.8172091617888804</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0.6705758433631502</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0.7547997154957112</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.65831054140569</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.7603398979500684</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>0.5669697880104639</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0.6145302218207954</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0.505982188986663</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.5697470750107609</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0.65831054140569</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0.583021933136167</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sff</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.9661412809060678</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>0.9069803774124751</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0.8585757865210202</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0.8748414065097995</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0.7603398979500684</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.583021933136167</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Coppia 1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Coppia 2</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>IoU</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>euclidean</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>dce</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>0.9108544260556372</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>euclidean</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ttc</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>0.8813162848196847</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>euclidean</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>eggert</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>0.8859761313668889</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>euclidean</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>time_eggert</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>0.7485057409870638</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>euclidean</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>0.5669697880104639</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>euclidean</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sff</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>0.9661412809060678</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dce</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ttc</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>0.8153509528750928</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dce</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>eggert</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>0.9059672685393528</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dce</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>time_eggert</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>0.8172091617888804</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dce</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>0.6145302218207954</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dce</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sff</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>0.9069803774124751</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ttc</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>eggert</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>0.850827181890391</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ttc</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>time_eggert</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>0.6705758433631502</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ttc</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>0.505982188986663</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ttc</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sff</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>0.8585757865210202</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>eggert</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>time_eggert</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>0.7547997154957112</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>eggert</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>0.5697470750107609</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>eggert</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sff</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>0.8748414065097995</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>time_eggert</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>0.65831054140569</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>time_eggert</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sff</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>0.7603398979500684</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sff</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>0.583021933136167</v>
       </c>
     </row>
   </sheetData>
